--- a/data/trans_orig/P57GLOBAL_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57GLOBAL_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2007</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2007 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>209028</t>
+          <t>209358</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>233782</t>
+          <t>233604</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>226989</t>
+          <t>227165</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>245479</t>
+          <t>246020</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>442038</t>
+          <t>442542</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>473911</t>
+          <t>472674</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,68%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38391</t>
+          <t>38569</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63145</t>
+          <t>62815</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15359</t>
+          <t>14818</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33849</t>
+          <t>33673</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59100</t>
+          <t>60337</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90973</t>
+          <t>90469</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>285803</t>
+          <t>284419</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>328972</t>
+          <t>330575</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>327879</t>
+          <t>328519</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>369296</t>
+          <t>367550</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>627999</t>
+          <t>624335</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>688124</t>
+          <t>683494</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>161267</t>
+          <t>159664</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>204436</t>
+          <t>205820</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>134653</t>
+          <t>136399</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>176070</t>
+          <t>175430</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>306064</t>
+          <t>310694</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>366189</t>
+          <t>369853</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,2%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>187162</t>
+          <t>187046</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>221135</t>
+          <t>221856</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>179933</t>
+          <t>176803</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>214973</t>
+          <t>213979</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>374040</t>
+          <t>375903</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>425747</t>
+          <t>424566</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>64,89%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97711</t>
+          <t>96990</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>131684</t>
+          <t>131800</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>120439</t>
+          <t>121433</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155479</t>
+          <t>158609</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>228511</t>
+          <t>229692</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>280218</t>
+          <t>278355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,55%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>242074</t>
+          <t>243776</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>276574</t>
+          <t>276242</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>248212</t>
+          <t>247288</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>281063</t>
+          <t>281009</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>501778</t>
+          <t>501780</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>548507</t>
+          <t>547428</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,98%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82097</t>
+          <t>82429</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>116597</t>
+          <t>114895</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90393</t>
+          <t>90447</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>123244</t>
+          <t>124168</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>181620</t>
+          <t>182699</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>228349</t>
+          <t>228347</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>151784</t>
+          <t>152696</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>175788</t>
+          <t>175809</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>167948</t>
+          <t>169044</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>187765</t>
+          <t>188305</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>327738</t>
+          <t>326947</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>357473</t>
+          <t>356598</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>86,98%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>27499</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51524</t>
+          <t>50612</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18908</t>
+          <t>18368</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38725</t>
+          <t>37629</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>52508</t>
+          <t>53383</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>82243</t>
+          <t>83034</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>178598</t>
+          <t>178994</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>208089</t>
+          <t>209533</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>189759</t>
+          <t>190600</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>218754</t>
+          <t>219080</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>377939</t>
+          <t>378112</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>419919</t>
+          <t>420428</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,59%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62722</t>
+          <t>61278</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>92213</t>
+          <t>91817</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59390</t>
+          <t>59064</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>88385</t>
+          <t>87544</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>129036</t>
+          <t>128527</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>171016</t>
+          <t>170843</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>306316</t>
+          <t>306393</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>355799</t>
+          <t>357057</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>291631</t>
+          <t>292548</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>341372</t>
+          <t>343080</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>615023</t>
+          <t>614174</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>684514</t>
+          <t>686318</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,81%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>259228</t>
+          <t>257970</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>308711</t>
+          <t>308634</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>295867</t>
+          <t>294159</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>345608</t>
+          <t>344691</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>567752</t>
+          <t>565948</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>637243</t>
+          <t>638092</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,95%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>596175</t>
+          <t>598006</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>637338</t>
+          <t>637039</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>671110</t>
+          <t>671063</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>707476</t>
+          <t>708091</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1280028</t>
+          <t>1280455</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1334522</t>
+          <t>1333922</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>104063</t>
+          <t>104362</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>145226</t>
+          <t>143395</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>74884</t>
+          <t>74269</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>111250</t>
+          <t>111297</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>189239</t>
+          <t>189839</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>243733</t>
+          <t>243306</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,97%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2250542</t>
+          <t>2250039</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2354164</t>
+          <t>2355032</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2385333</t>
+          <t>2385562</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2485211</t>
+          <t>2491086</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4661791</t>
+          <t>4665905</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4811229</t>
+          <t>4815066</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,44%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>916312</t>
+          <t>915444</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1019934</t>
+          <t>1020437</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>890860</t>
+          <t>884985</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>990738</t>
+          <t>990509</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1835319</t>
+          <t>1831482</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1984757</t>
+          <t>1980643</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2012</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2012 (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>207274</t>
+          <t>207546</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>236692</t>
+          <t>238115</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>225730</t>
+          <t>226080</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>249101</t>
+          <t>249764</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>441452</t>
+          <t>442982</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>479233</t>
+          <t>479994</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45962</t>
+          <t>44539</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75380</t>
+          <t>75108</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28262</t>
+          <t>27599</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51633</t>
+          <t>51283</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80784</t>
+          <t>80023</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118565</t>
+          <t>117035</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>261306</t>
+          <t>260127</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>304969</t>
+          <t>307704</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>283057</t>
+          <t>282742</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>329699</t>
+          <t>329122</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>555173</t>
+          <t>554805</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>622155</t>
+          <t>622183</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>197584</t>
+          <t>194849</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>241247</t>
+          <t>242426</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>192871</t>
+          <t>193448</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>239513</t>
+          <t>239828</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>402968</t>
+          <t>402940</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>469950</t>
+          <t>470318</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,88%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>195422</t>
+          <t>197610</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>230041</t>
+          <t>230130</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>240828</t>
+          <t>241986</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>272740</t>
+          <t>271944</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>448023</t>
+          <t>446403</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>494174</t>
+          <t>496258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>75,09%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92978</t>
+          <t>92889</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127597</t>
+          <t>125409</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65115</t>
+          <t>65911</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97027</t>
+          <t>95869</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>166700</t>
+          <t>164616</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>212851</t>
+          <t>214471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>179840</t>
+          <t>181304</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>218555</t>
+          <t>220903</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>224915</t>
+          <t>224750</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>263978</t>
+          <t>264255</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>417404</t>
+          <t>416405</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>472613</t>
+          <t>472928</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,42%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>152149</t>
+          <t>149801</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>190864</t>
+          <t>189400</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>122991</t>
+          <t>122714</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>162054</t>
+          <t>162219</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>285060</t>
+          <t>284745</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>340269</t>
+          <t>341268</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>45,04%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>108708</t>
+          <t>107888</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>137694</t>
+          <t>137534</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>148699</t>
+          <t>148750</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>174835</t>
+          <t>175455</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>263853</t>
+          <t>264511</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>305429</t>
+          <t>304195</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>70,69%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73909</t>
+          <t>74069</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102895</t>
+          <t>103715</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43863</t>
+          <t>43243</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69999</t>
+          <t>69948</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>124873</t>
+          <t>126107</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>166449</t>
+          <t>165791</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,53%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>160690</t>
+          <t>160608</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>192553</t>
+          <t>191286</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>202150</t>
+          <t>201646</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>230376</t>
+          <t>229294</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>367456</t>
+          <t>367927</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>413419</t>
+          <t>411246</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,36%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>76230</t>
+          <t>77497</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>108093</t>
+          <t>108175</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46526</t>
+          <t>47608</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>74752</t>
+          <t>75256</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>132266</t>
+          <t>134439</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>178229</t>
+          <t>177758</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,58%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>378706</t>
+          <t>377647</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>431298</t>
+          <t>428193</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>464062</t>
+          <t>465030</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>510997</t>
+          <t>512682</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>858305</t>
+          <t>857001</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>927532</t>
+          <t>927140</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,4%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>222628</t>
+          <t>225733</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>275220</t>
+          <t>276279</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>170940</t>
+          <t>169255</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>217875</t>
+          <t>216907</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>408331</t>
+          <t>408723</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>477558</t>
+          <t>478862</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,85%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>689226</t>
+          <t>689543</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>721036</t>
+          <t>720784</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>716792</t>
+          <t>719267</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>755391</t>
+          <t>754712</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1418180</t>
+          <t>1419641</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1467711</t>
+          <t>1467239</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,06%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>52072</t>
+          <t>52324</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>83882</t>
+          <t>83565</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>65219</t>
+          <t>65898</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>103818</t>
+          <t>101343</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>126008</t>
+          <t>126480</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>175539</t>
+          <t>174078</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2280017</t>
+          <t>2278392</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2384626</t>
+          <t>2391339</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2596683</t>
+          <t>2599356</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2703225</t>
+          <t>2702639</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4901721</t>
+          <t>4910688</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5060829</t>
+          <t>5064090</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,29%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1001726</t>
+          <t>995013</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1106335</t>
+          <t>1107960</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>819678</t>
+          <t>820264</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>926220</t>
+          <t>923547</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1848426</t>
+          <t>1845165</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2007534</t>
+          <t>1998567</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2016</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2016 (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>228722</t>
+          <t>227904</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>253669</t>
+          <t>253978</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>229702</t>
+          <t>227992</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>252676</t>
+          <t>251897</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>463442</t>
+          <t>466978</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>500628</t>
+          <t>499964</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,14%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32207</t>
+          <t>31898</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57154</t>
+          <t>57972</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28703</t>
+          <t>29482</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51677</t>
+          <t>53387</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66627</t>
+          <t>67291</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103813</t>
+          <t>100277</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>397785</t>
+          <t>394815</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>429954</t>
+          <t>430007</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>410637</t>
+          <t>409639</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>444764</t>
+          <t>444419</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>819380</t>
+          <t>819461</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>867549</t>
+          <t>865268</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,25%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67419</t>
+          <t>67366</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>99588</t>
+          <t>102558</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72895</t>
+          <t>73240</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107022</t>
+          <t>108020</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>147482</t>
+          <t>149763</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>195651</t>
+          <t>195570</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>233758</t>
+          <t>234440</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>263427</t>
+          <t>262906</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>263361</t>
+          <t>262340</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>289387</t>
+          <t>287505</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>504863</t>
+          <t>504699</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>544158</t>
+          <t>542049</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,45%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53232</t>
+          <t>53753</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82901</t>
+          <t>82219</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43479</t>
+          <t>45361</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69505</t>
+          <t>70526</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>105367</t>
+          <t>107476</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144662</t>
+          <t>144826</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>156910</t>
+          <t>154453</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>196092</t>
+          <t>193491</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>205800</t>
+          <t>205047</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>243810</t>
+          <t>243331</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>370685</t>
+          <t>369859</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>427552</t>
+          <t>428363</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,95%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>171847</t>
+          <t>174448</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>211029</t>
+          <t>213486</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>140488</t>
+          <t>140967</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>178498</t>
+          <t>179251</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>324685</t>
+          <t>323874</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>381552</t>
+          <t>382378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,83%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>181943</t>
+          <t>182090</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>198753</t>
+          <t>198748</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>191044</t>
+          <t>191187</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>206933</t>
+          <t>207149</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>379190</t>
+          <t>379695</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>402681</t>
+          <t>402712</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11402</t>
+          <t>11407</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28212</t>
+          <t>28065</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11654</t>
+          <t>11438</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27543</t>
+          <t>27400</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26061</t>
+          <t>26030</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49552</t>
+          <t>49047</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>195858</t>
+          <t>195628</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>222118</t>
+          <t>221494</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>206575</t>
+          <t>208558</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>232688</t>
+          <t>233139</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>411355</t>
+          <t>409885</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>446686</t>
+          <t>447377</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,73%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>41629</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67265</t>
+          <t>67495</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38488</t>
+          <t>38037</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>64601</t>
+          <t>62618</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>87613</t>
+          <t>86922</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>122944</t>
+          <t>124414</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>534128</t>
+          <t>532025</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>571350</t>
+          <t>572591</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>584202</t>
+          <t>584402</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>618188</t>
+          <t>617481</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1130760</t>
+          <t>1131314</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1181339</t>
+          <t>1180842</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,66%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>80580</t>
+          <t>79339</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>117802</t>
+          <t>119905</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>61808</t>
+          <t>62515</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>95794</t>
+          <t>95594</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>150587</t>
+          <t>151084</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>201166</t>
+          <t>200612</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>706481</t>
+          <t>705370</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>734219</t>
+          <t>735402</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>767023</t>
+          <t>767442</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>793399</t>
+          <t>792952</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1481428</t>
+          <t>1481328</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1519856</t>
+          <t>1521897</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>40717</t>
+          <t>39534</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>68455</t>
+          <t>69566</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29405</t>
+          <t>29852</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>55781</t>
+          <t>55362</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>77884</t>
+          <t>75843</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>116312</t>
+          <t>116412</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2717762</t>
+          <t>2709949</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2808146</t>
+          <t>2805215</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,82 +10138,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>83,29%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>2788</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>2975000</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>2929722</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3018733</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>84,79%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>86,03%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>5414</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>5733599</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>5672689</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>5791798</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>83,38%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2788</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>2975000</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>2924839</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>3015188</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>84,79%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>83,36%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>85,93%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>5414</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>5733599</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>5669921</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>5799050</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>83,38%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,22%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>559846</t>
+          <t>562777</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>650230</t>
+          <t>658043</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,82 +10251,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>16,71%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>19,54%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>533764</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>490031</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>579042</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>15,21%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>13,97%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>16,5%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>1143157</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>1084958</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>1204067</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>16,62%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>19,31%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>533764</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>493576</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>583925</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>15,21%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>14,07%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>16,64%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>1099</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>1143157</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>1077706</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>1206835</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>16,62%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2023</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2023 (tasa de respuesta: 98,07%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>141127</t>
+          <t>141351</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>185913</t>
+          <t>185052</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>158185</t>
+          <t>158717</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>185918</t>
+          <t>185408</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>311196</t>
+          <t>310731</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>362498</t>
+          <t>362863</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,17%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120925</t>
+          <t>121786</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>165711</t>
+          <t>165487</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>100468</t>
+          <t>100978</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128201</t>
+          <t>127669</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>230726</t>
+          <t>230361</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>282028</t>
+          <t>282493</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,62%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>299439</t>
+          <t>293952</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>354567</t>
+          <t>353340</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>274767</t>
+          <t>274203</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>314083</t>
+          <t>315155</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>584012</t>
+          <t>585301</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>654858</t>
+          <t>656389</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,98%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>159370</t>
+          <t>160597</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>214498</t>
+          <t>219985</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>197834</t>
+          <t>196762</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>237150</t>
+          <t>237714</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>370996</t>
+          <t>369465</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>441842</t>
+          <t>440553</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,94%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>127249</t>
+          <t>126174</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>160909</t>
+          <t>161607</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>159937</t>
+          <t>157350</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>189775</t>
+          <t>187985</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>293092</t>
+          <t>296624</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>339256</t>
+          <t>341637</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,76%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135870</t>
+          <t>135172</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>169530</t>
+          <t>170605</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>126186</t>
+          <t>127976</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156024</t>
+          <t>158611</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>273484</t>
+          <t>271103</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>319648</t>
+          <t>316116</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>51,59%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84560</t>
+          <t>84697</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126702</t>
+          <t>127314</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80998</t>
+          <t>83048</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>174892</t>
+          <t>170882</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170694</t>
+          <t>172473</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>281237</t>
+          <t>280307</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,28%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>181712</t>
+          <t>181100</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>223854</t>
+          <t>223717</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>289290</t>
+          <t>293300</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>383184</t>
+          <t>381134</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>491359</t>
+          <t>492289</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>601902</t>
+          <t>600123</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,68%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>157116</t>
+          <t>156333</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>170548</t>
+          <t>170676</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>185170</t>
+          <t>185531</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>197359</t>
+          <t>197280</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>345952</t>
+          <t>346099</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>365330</t>
+          <t>364972</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,47%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20942</t>
+          <t>21725</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10915</t>
+          <t>10994</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23104</t>
+          <t>22743</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21002</t>
+          <t>21360</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40380</t>
+          <t>40233</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>95336</t>
+          <t>95320</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123649</t>
+          <t>123231</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>93680</t>
+          <t>92908</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>117301</t>
+          <t>118117</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>194379</t>
+          <t>195768</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>233030</t>
+          <t>236088</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,94%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>145001</t>
+          <t>145419</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>173314</t>
+          <t>173330</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>139362</t>
+          <t>138546</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>162983</t>
+          <t>163755</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>292283</t>
+          <t>289225</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>330934</t>
+          <t>329545</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>62,73%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>373636</t>
+          <t>372863</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>430238</t>
+          <t>427035</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>391989</t>
+          <t>392033</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>439682</t>
+          <t>439966</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>778662</t>
+          <t>779252</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>849471</t>
+          <t>855675</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,77%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>182957</t>
+          <t>186160</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>239559</t>
+          <t>240332</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>191433</t>
+          <t>191149</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>239126</t>
+          <t>239082</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>394839</t>
+          <t>388635</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>465648</t>
+          <t>465058</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,37%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>255598</t>
+          <t>272940</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>798506</t>
+          <t>800012</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>614076</t>
+          <t>613484</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>645079</t>
+          <t>645193</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>758285</t>
+          <t>683443</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1435830</t>
+          <t>1436271</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>126642</t>
+          <t>125136</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>669550</t>
+          <t>652208</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>70381</t>
+          <t>70267</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>101384</t>
+          <t>101976</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>204778</t>
+          <t>204337</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>882323</t>
+          <t>957165</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>58,34%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1518941</t>
+          <t>1494593</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2174881</t>
+          <t>2170174</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1980925</t>
+          <t>1955444</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2201273</t>
+          <t>2194019</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3520377</t>
+          <t>3527222</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4320061</t>
+          <t>4322024</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,55%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1236137</t>
+          <t>1240844</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1892077</t>
+          <t>1916425</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1188685</t>
+          <t>1195939</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1409033</t>
+          <t>1434514</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2480916</t>
+          <t>2478953</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3280600</t>
+          <t>3273755</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,14%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57GLOBAL_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57GLOBAL_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>209358</t>
+          <t>207728</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>233604</t>
+          <t>232976</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>227165</t>
+          <t>226731</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>246020</t>
+          <t>245211</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>442542</t>
+          <t>443562</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>472674</t>
+          <t>473793</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,89%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38569</t>
+          <t>39197</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62815</t>
+          <t>64445</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14818</t>
+          <t>15627</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33673</t>
+          <t>34107</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>60337</t>
+          <t>59218</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90469</t>
+          <t>89449</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>284419</t>
+          <t>287331</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>330575</t>
+          <t>331943</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>328519</t>
+          <t>330512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>367550</t>
+          <t>370387</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>624335</t>
+          <t>627567</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>683494</t>
+          <t>688972</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>69,3%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>159664</t>
+          <t>158296</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>205820</t>
+          <t>202908</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>136399</t>
+          <t>133562</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>175430</t>
+          <t>173437</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>310694</t>
+          <t>305216</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>369853</t>
+          <t>366621</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>36,88%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>187046</t>
+          <t>186720</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>221856</t>
+          <t>221672</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>176803</t>
+          <t>176856</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>213979</t>
+          <t>212714</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>375903</t>
+          <t>377562</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>424566</t>
+          <t>424538</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96990</t>
+          <t>97174</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>131800</t>
+          <t>132126</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121433</t>
+          <t>122698</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158609</t>
+          <t>158556</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>229692</t>
+          <t>229720</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>278355</t>
+          <t>276696</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,29%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>243776</t>
+          <t>243787</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>276242</t>
+          <t>276313</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>247288</t>
+          <t>245759</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>281009</t>
+          <t>280899</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>501780</t>
+          <t>500094</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>547428</t>
+          <t>546323</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,83%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82429</t>
+          <t>82358</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114895</t>
+          <t>114884</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90447</t>
+          <t>90557</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124168</t>
+          <t>125697</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>182699</t>
+          <t>183804</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>228347</t>
+          <t>230033</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,51%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>152696</t>
+          <t>153092</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>175809</t>
+          <t>175688</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>169044</t>
+          <t>168105</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>188305</t>
+          <t>188018</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>326947</t>
+          <t>328003</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>356598</t>
+          <t>358427</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,43%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27499</t>
+          <t>27620</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50612</t>
+          <t>50216</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18368</t>
+          <t>18655</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37629</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>53383</t>
+          <t>51554</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>83034</t>
+          <t>81978</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>178994</t>
+          <t>178005</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>209533</t>
+          <t>208734</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>190600</t>
+          <t>189424</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>219080</t>
+          <t>218680</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>378112</t>
+          <t>377963</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>420428</t>
+          <t>420289</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,56%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61278</t>
+          <t>62077</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91817</t>
+          <t>92806</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59064</t>
+          <t>59464</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>87544</t>
+          <t>88720</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>128527</t>
+          <t>128666</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>170843</t>
+          <t>170992</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,15%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>306393</t>
+          <t>304341</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>357057</t>
+          <t>354617</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>292548</t>
+          <t>292089</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>343080</t>
+          <t>344049</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>614174</t>
+          <t>612293</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>686318</t>
+          <t>685304</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,73%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>257970</t>
+          <t>260410</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>308634</t>
+          <t>310686</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>294159</t>
+          <t>293190</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>344691</t>
+          <t>345150</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>565948</t>
+          <t>566962</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>638092</t>
+          <t>639973</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>51,11%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>598006</t>
+          <t>594046</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>637039</t>
+          <t>635373</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>671063</t>
+          <t>673076</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>708091</t>
+          <t>706623</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1280455</t>
+          <t>1278449</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1333922</t>
+          <t>1331853</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,41%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>104362</t>
+          <t>106028</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>143395</t>
+          <t>147355</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>74269</t>
+          <t>75737</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>111297</t>
+          <t>109284</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>189839</t>
+          <t>191908</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>243306</t>
+          <t>245312</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2250039</t>
+          <t>2246459</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2355032</t>
+          <t>2354550</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2385562</t>
+          <t>2391150</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2491086</t>
+          <t>2493440</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4665905</t>
+          <t>4670773</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4815066</t>
+          <t>4816316</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,46%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>915444</t>
+          <t>915926</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1020437</t>
+          <t>1024017</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>884985</t>
+          <t>882631</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>990509</t>
+          <t>984921</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1831482</t>
+          <t>1830232</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1980643</t>
+          <t>1975775</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>207546</t>
+          <t>208809</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>238115</t>
+          <t>238332</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>226080</t>
+          <t>224846</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>249764</t>
+          <t>249545</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>442982</t>
+          <t>442270</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>479994</t>
+          <t>480020</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,72%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44539</t>
+          <t>44322</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75108</t>
+          <t>73845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27599</t>
+          <t>27818</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51283</t>
+          <t>52517</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80023</t>
+          <t>79997</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117035</t>
+          <t>117747</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>260127</t>
+          <t>260553</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>307704</t>
+          <t>307479</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>282742</t>
+          <t>281848</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>329122</t>
+          <t>329789</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>554805</t>
+          <t>559021</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>622183</t>
+          <t>622236</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,7%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>194849</t>
+          <t>195074</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>242426</t>
+          <t>242000</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>193448</t>
+          <t>192781</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>239828</t>
+          <t>240722</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>402940</t>
+          <t>402887</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>470318</t>
+          <t>466102</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>45,47%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>197610</t>
+          <t>196629</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>230130</t>
+          <t>231178</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>241986</t>
+          <t>241806</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>271944</t>
+          <t>274142</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>446403</t>
+          <t>449764</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>496258</t>
+          <t>494316</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,8%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92889</t>
+          <t>91841</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>125409</t>
+          <t>126390</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65911</t>
+          <t>63713</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95869</t>
+          <t>96049</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>164616</t>
+          <t>166558</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>214471</t>
+          <t>211110</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>181304</t>
+          <t>180748</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>220903</t>
+          <t>219970</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>224750</t>
+          <t>226924</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>264255</t>
+          <t>263711</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>416405</t>
+          <t>417307</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>472928</t>
+          <t>471687</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,25%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149801</t>
+          <t>150734</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>189400</t>
+          <t>189956</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>122714</t>
+          <t>123258</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>162219</t>
+          <t>160045</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>284745</t>
+          <t>285986</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>341268</t>
+          <t>340366</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>44,92%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107888</t>
+          <t>108076</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>137534</t>
+          <t>136810</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>148750</t>
+          <t>147150</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>175455</t>
+          <t>173723</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>264511</t>
+          <t>263967</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>304195</t>
+          <t>303325</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,49%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74069</t>
+          <t>74793</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>103715</t>
+          <t>103527</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43243</t>
+          <t>44975</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69948</t>
+          <t>71548</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>126107</t>
+          <t>126977</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>165791</t>
+          <t>166335</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>160608</t>
+          <t>157654</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>191286</t>
+          <t>190501</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>201646</t>
+          <t>200809</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>229294</t>
+          <t>227686</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>367927</t>
+          <t>369424</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>411246</t>
+          <t>412536</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,6%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>77497</t>
+          <t>78282</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>108175</t>
+          <t>111129</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47608</t>
+          <t>49216</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>75256</t>
+          <t>76093</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>134439</t>
+          <t>133149</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>177758</t>
+          <t>176261</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>377647</t>
+          <t>378860</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>428193</t>
+          <t>429334</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>465030</t>
+          <t>464386</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>512682</t>
+          <t>513205</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>857001</t>
+          <t>855506</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>927140</t>
+          <t>927796</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,45%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>225733</t>
+          <t>224592</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>276279</t>
+          <t>275066</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>169255</t>
+          <t>168732</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>216907</t>
+          <t>217551</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>408723</t>
+          <t>408067</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>478862</t>
+          <t>480357</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,96%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>689543</t>
+          <t>688898</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>720784</t>
+          <t>720185</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>719267</t>
+          <t>717560</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>754712</t>
+          <t>754796</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1419641</t>
+          <t>1421766</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1467239</t>
+          <t>1467830</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,1%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>52324</t>
+          <t>52923</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>83565</t>
+          <t>84210</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>65898</t>
+          <t>65814</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>101343</t>
+          <t>103050</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>126480</t>
+          <t>125889</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>174078</t>
+          <t>171953</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2278392</t>
+          <t>2276496</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2391339</t>
+          <t>2387681</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2599356</t>
+          <t>2603273</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2702639</t>
+          <t>2701715</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4910688</t>
+          <t>4908312</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5064090</t>
+          <t>5063081</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,28%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>995013</t>
+          <t>998671</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1107960</t>
+          <t>1109856</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>820264</t>
+          <t>821188</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>923547</t>
+          <t>919630</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1845165</t>
+          <t>1846174</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1998567</t>
+          <t>2000943</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>227904</t>
+          <t>227315</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>253978</t>
+          <t>252625</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>227992</t>
+          <t>226995</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>251897</t>
+          <t>252291</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>466978</t>
+          <t>465749</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>499964</t>
+          <t>499443</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31898</t>
+          <t>33251</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57972</t>
+          <t>58561</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29482</t>
+          <t>29088</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53387</t>
+          <t>54384</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>67291</t>
+          <t>67812</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100277</t>
+          <t>101506</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>394815</t>
+          <t>396966</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>430007</t>
+          <t>430315</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>409639</t>
+          <t>412484</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>444419</t>
+          <t>445611</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>819461</t>
+          <t>818783</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>865268</t>
+          <t>865087</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,23%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67366</t>
+          <t>67058</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102558</t>
+          <t>100407</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73240</t>
+          <t>72048</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108020</t>
+          <t>105175</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>149763</t>
+          <t>149944</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>195570</t>
+          <t>196248</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>234440</t>
+          <t>234210</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>262906</t>
+          <t>262505</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>262340</t>
+          <t>262184</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>287505</t>
+          <t>288527</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>504699</t>
+          <t>503472</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>542049</t>
+          <t>543632</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,7%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53753</t>
+          <t>54154</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82219</t>
+          <t>82449</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45361</t>
+          <t>44339</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70526</t>
+          <t>70682</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>107476</t>
+          <t>105893</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144826</t>
+          <t>146053</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>154453</t>
+          <t>156687</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>193491</t>
+          <t>197348</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>205047</t>
+          <t>204559</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>243331</t>
+          <t>245053</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>369859</t>
+          <t>373035</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>428363</t>
+          <t>429183</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>57,05%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>174448</t>
+          <t>170591</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>213486</t>
+          <t>211252</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>140967</t>
+          <t>139245</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>179251</t>
+          <t>179739</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>323874</t>
+          <t>323054</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>382378</t>
+          <t>379202</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,41%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>182090</t>
+          <t>181617</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>198748</t>
+          <t>198302</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>191187</t>
+          <t>190732</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>207149</t>
+          <t>207743</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>379695</t>
+          <t>379196</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>402712</t>
+          <t>401868</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>11853</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28065</t>
+          <t>28538</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11438</t>
+          <t>10844</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27400</t>
+          <t>27855</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26030</t>
+          <t>26874</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49047</t>
+          <t>49546</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>195628</t>
+          <t>195927</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>221494</t>
+          <t>221036</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>208558</t>
+          <t>205864</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>233139</t>
+          <t>232330</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>409885</t>
+          <t>409401</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>447377</t>
+          <t>446184</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,51%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41629</t>
+          <t>42087</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67495</t>
+          <t>67196</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38037</t>
+          <t>38846</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62618</t>
+          <t>65312</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86922</t>
+          <t>88115</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>124414</t>
+          <t>124898</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>532025</t>
+          <t>534645</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>572591</t>
+          <t>572099</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>584402</t>
+          <t>584899</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>617481</t>
+          <t>618282</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1131314</t>
+          <t>1127698</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1180842</t>
+          <t>1181878</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,73%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>79339</t>
+          <t>79831</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>119905</t>
+          <t>117285</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>62515</t>
+          <t>61714</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>95594</t>
+          <t>95097</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>151084</t>
+          <t>150048</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>200612</t>
+          <t>204228</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>705370</t>
+          <t>705450</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>735402</t>
+          <t>733911</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>767442</t>
+          <t>766162</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>792952</t>
+          <t>792772</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1481328</t>
+          <t>1481677</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1521897</t>
+          <t>1519271</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39534</t>
+          <t>41025</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>69566</t>
+          <t>69486</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29852</t>
+          <t>30032</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>55362</t>
+          <t>56642</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>75843</t>
+          <t>78469</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>116412</t>
+          <t>116063</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2709949</t>
+          <t>2710225</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2805215</t>
+          <t>2804228</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2929722</t>
+          <t>2925991</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3018733</t>
+          <t>3014856</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5672689</t>
+          <t>5663488</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5791798</t>
+          <t>5792360</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>562777</t>
+          <t>563764</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>658043</t>
+          <t>657767</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>490031</t>
+          <t>493908</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>579042</t>
+          <t>582773</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1084958</t>
+          <t>1084396</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1204067</t>
+          <t>1213268</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>163669</t>
+          <t>176498</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>141351</t>
+          <t>157071</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>185052</t>
+          <t>195620</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>172655</t>
+          <t>189723</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>158717</t>
+          <t>175326</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>185408</t>
+          <t>204142</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>336324</t>
+          <t>366221</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>310731</t>
+          <t>342201</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>362863</t>
+          <t>390288</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>62,36%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>143169</t>
+          <t>138124</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>121786</t>
+          <t>119002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>165487</t>
+          <t>157551</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>113731</t>
+          <t>121472</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>100978</t>
+          <t>107053</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127669</t>
+          <t>135869</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>256900</t>
+          <t>259596</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>230361</t>
+          <t>235529</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>282493</t>
+          <t>283616</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>45,32%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>306838</t>
+          <t>314622</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>306838</t>
+          <t>314622</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>306838</t>
+          <t>314622</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>286386</t>
+          <t>311195</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>286386</t>
+          <t>311195</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>286386</t>
+          <t>311195</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>593224</t>
+          <t>625817</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>593224</t>
+          <t>625817</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>593224</t>
+          <t>625817</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>325567</t>
+          <t>334220</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>293952</t>
+          <t>304348</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>353340</t>
+          <t>359031</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>295479</t>
+          <t>315202</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>274203</t>
+          <t>294416</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>315155</t>
+          <t>335833</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>621046</t>
+          <t>649421</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>585301</t>
+          <t>610876</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>656389</t>
+          <t>683850</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>64,01%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>188370</t>
+          <t>190731</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>160597</t>
+          <t>165920</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>219985</t>
+          <t>220603</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>216438</t>
+          <t>228179</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>196762</t>
+          <t>207548</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>237714</t>
+          <t>248965</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>404808</t>
+          <t>418911</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>369465</t>
+          <t>384482</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>440553</t>
+          <t>457456</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,82%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>513937</t>
+          <t>524951</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>513937</t>
+          <t>524951</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>513937</t>
+          <t>524951</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511917</t>
+          <t>543381</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511917</t>
+          <t>543381</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511917</t>
+          <t>543381</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1025854</t>
+          <t>1068332</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1025854</t>
+          <t>1068332</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1025854</t>
+          <t>1068332</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>143821</t>
+          <t>146044</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>126174</t>
+          <t>128970</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>161607</t>
+          <t>163124</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>173868</t>
+          <t>181879</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>157350</t>
+          <t>167194</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>187985</t>
+          <t>197848</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>317689</t>
+          <t>327923</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>296624</t>
+          <t>306104</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>341637</t>
+          <t>351815</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>56,55%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>152958</t>
+          <t>151270</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135172</t>
+          <t>134190</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>170605</t>
+          <t>168344</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>142093</t>
+          <t>142927</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127976</t>
+          <t>126958</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158611</t>
+          <t>157612</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>295051</t>
+          <t>294197</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>271103</t>
+          <t>270305</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>316116</t>
+          <t>316016</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>50,8%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>296779</t>
+          <t>297314</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>296779</t>
+          <t>297314</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>296779</t>
+          <t>297314</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>315961</t>
+          <t>324806</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>315961</t>
+          <t>324806</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>315961</t>
+          <t>324806</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>612740</t>
+          <t>622120</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>612740</t>
+          <t>622120</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>612740</t>
+          <t>622120</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>104296</t>
+          <t>126814</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84697</t>
+          <t>104921</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127314</t>
+          <t>152398</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>134707</t>
+          <t>153731</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83048</t>
+          <t>136043</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>170882</t>
+          <t>173658</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>239003</t>
+          <t>280544</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>172473</t>
+          <t>250927</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>280307</t>
+          <t>312456</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>40,24%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>204118</t>
+          <t>240105</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>181100</t>
+          <t>214521</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>223717</t>
+          <t>261998</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>329475</t>
+          <t>255905</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>293300</t>
+          <t>235978</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>381134</t>
+          <t>273593</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>533593</t>
+          <t>496010</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>492289</t>
+          <t>464098</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>600123</t>
+          <t>525627</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>308414</t>
+          <t>366919</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>308414</t>
+          <t>366919</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>308414</t>
+          <t>366919</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>464182</t>
+          <t>409636</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>464182</t>
+          <t>409636</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>464182</t>
+          <t>409636</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>772596</t>
+          <t>776554</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>772596</t>
+          <t>776554</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>772596</t>
+          <t>776554</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>165395</t>
+          <t>188955</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>156333</t>
+          <t>179448</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>170676</t>
+          <t>195217</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>192391</t>
+          <t>210496</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>185531</t>
+          <t>202594</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>197280</t>
+          <t>216000</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>357786</t>
+          <t>399451</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>346099</t>
+          <t>388801</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>364972</t>
+          <t>409317</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,8%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>15975</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7382</t>
+          <t>9713</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21725</t>
+          <t>25482</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15883</t>
+          <t>16327</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10994</t>
+          <t>10823</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22743</t>
+          <t>24229</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>28546</t>
+          <t>32302</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21360</t>
+          <t>22436</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40233</t>
+          <t>42952</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178058</t>
+          <t>204930</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178058</t>
+          <t>204930</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178058</t>
+          <t>204930</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386332</t>
+          <t>431753</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386332</t>
+          <t>431753</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386332</t>
+          <t>431753</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>108964</t>
+          <t>115116</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>95320</t>
+          <t>101687</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123231</t>
+          <t>131906</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>105239</t>
+          <t>111090</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>92908</t>
+          <t>98657</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>118117</t>
+          <t>123821</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>214203</t>
+          <t>226205</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>195768</t>
+          <t>206475</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>236088</t>
+          <t>243713</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>45,72%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>159686</t>
+          <t>154606</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>145419</t>
+          <t>137816</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>173330</t>
+          <t>168035</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>151424</t>
+          <t>152251</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>138546</t>
+          <t>139520</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>163755</t>
+          <t>164684</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>311110</t>
+          <t>306858</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>289225</t>
+          <t>289350</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>329545</t>
+          <t>326588</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>61,27%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>268650</t>
+          <t>269722</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>268650</t>
+          <t>269722</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>268650</t>
+          <t>269722</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256663</t>
+          <t>263341</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256663</t>
+          <t>263341</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256663</t>
+          <t>263341</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>525313</t>
+          <t>533063</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>525313</t>
+          <t>533063</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>525313</t>
+          <t>533063</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>401914</t>
+          <t>469497</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>372863</t>
+          <t>442355</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>427035</t>
+          <t>501304</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>415313</t>
+          <t>501340</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>392033</t>
+          <t>477099</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>439966</t>
+          <t>525281</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>817228</t>
+          <t>970837</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>779252</t>
+          <t>927629</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>855675</t>
+          <t>1010035</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>69,08%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>211281</t>
+          <t>237178</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>186160</t>
+          <t>205371</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>240332</t>
+          <t>264320</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>215802</t>
+          <t>254054</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>191149</t>
+          <t>230113</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>239082</t>
+          <t>278295</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>427082</t>
+          <t>491232</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>388635</t>
+          <t>452034</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>465058</t>
+          <t>534440</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>613195</t>
+          <t>706675</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>613195</t>
+          <t>706675</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>613195</t>
+          <t>706675</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>631115</t>
+          <t>755394</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>631115</t>
+          <t>755394</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>631115</t>
+          <t>755394</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1244310</t>
+          <t>1462069</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1244310</t>
+          <t>1462069</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1244310</t>
+          <t>1462069</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>582845</t>
+          <t>681061</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>272940</t>
+          <t>656816</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>800012</t>
+          <t>701410</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>630412</t>
+          <t>728874</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>613484</t>
+          <t>711942</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>645193</t>
+          <t>746268</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1213257</t>
+          <t>1409935</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>683443</t>
+          <t>1381024</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1436271</t>
+          <t>1437692</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>88,63%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>342303</t>
+          <t>113086</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>125136</t>
+          <t>92737</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>652208</t>
+          <t>137331</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>85048</t>
+          <t>99161</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>70267</t>
+          <t>81767</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>101976</t>
+          <t>116093</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>427351</t>
+          <t>212247</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>204337</t>
+          <t>184490</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>957165</t>
+          <t>241158</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>925148</t>
+          <t>794147</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>925148</t>
+          <t>794147</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>925148</t>
+          <t>794147</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715460</t>
+          <t>828035</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715460</t>
+          <t>828035</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715460</t>
+          <t>828035</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1640608</t>
+          <t>1622182</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1640608</t>
+          <t>1622182</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1640608</t>
+          <t>1622182</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1996471</t>
+          <t>2238205</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1494593</t>
+          <t>2176876</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2170174</t>
+          <t>2301574</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2120065</t>
+          <t>2392335</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1955444</t>
+          <t>2340477</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2194019</t>
+          <t>2443956</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4116536</t>
+          <t>4630539</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3527222</t>
+          <t>4547219</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4322024</t>
+          <t>4719049</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>66,08%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1414547</t>
+          <t>1241076</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1240844</t>
+          <t>1177707</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1916425</t>
+          <t>1302405</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1269893</t>
+          <t>1270276</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1195939</t>
+          <t>1218655</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1434514</t>
+          <t>1322134</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2684441</t>
+          <t>2511352</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2478953</t>
+          <t>2422842</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3273755</t>
+          <t>2594672</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3411018</t>
+          <t>3479281</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3411018</t>
+          <t>3479281</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3411018</t>
+          <t>3479281</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3389958</t>
+          <t>3662611</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3389958</t>
+          <t>3662611</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3389958</t>
+          <t>3662611</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6800977</t>
+          <t>7141891</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6800977</t>
+          <t>7141891</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6800977</t>
+          <t>7141891</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
